--- a/DataAnalysis/TryingToPackStuffBetter/PreprocessingRTandDIM/CI/0.05/Results.xlsx
+++ b/DataAnalysis/TryingToPackStuffBetter/PreprocessingRTandDIM/CI/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\TryingToPackStuffBetter\PreprocessingRTandDIM\CI\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D505D7-FCCF-4FE1-AA9C-A620E2194BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33774DA-C667-40F4-B333-E4C027E1651D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -203,7 +203,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -528,34 +528,34 @@
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>16.722222222222221</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <v>2.635231383473652</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="3">
         <v>22.166666666666668</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="3">
         <v>5.2380817099392409</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="3">
         <v>31.5</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="3">
         <v>3.2691742076555053</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="3">
         <v>23.462962962962958</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="3">
         <v>2.8096779394544562</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="3">
         <v>7.5740740740740744</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="3">
         <v>0.90948364131916359</v>
       </c>
     </row>
@@ -563,34 +563,34 @@
       <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>17.333333333333332</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>3.2812599206199211</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="3">
         <v>21.083333333333332</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="3">
         <v>2.1544527534078504</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="3">
         <v>30.833333333333332</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="3">
         <v>2.0655911179772892</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="3">
         <v>23.083333333333332</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="3">
         <v>0.67288764127287815</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="3">
         <v>6.583333333333333</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="3">
         <v>2.2329601678290456</v>
       </c>
     </row>
@@ -598,34 +598,34 @@
       <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>17.214285714285715</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <v>2.6276913640612221</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="3">
         <v>22.214285714285715</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="3">
         <v>2.3954321610296625</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="3">
         <v>30.214285714285715</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="3">
         <v>2.03832330722138</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="3">
         <v>23.214285714285715</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="3">
         <v>0.55872113989835059</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="3">
         <v>6.1428571428571432</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="3">
         <v>2.2161623725204915</v>
       </c>
     </row>
@@ -633,39 +633,49 @@
       <c r="B6" t="s">
         <v>35</v>
       </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="3">
         <v>16</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3">
         <v>1.5491933384829668</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="3">
         <v>18.916666666666668</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="3">
         <v>1.8551729479125838</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="3">
         <v>31</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="3">
         <v>2.4289915602982237</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="3">
         <v>21.972222222222225</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="3">
         <v>0.41387956738198212</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="3">
         <v>6.0555555555555562</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="3">
         <v>1.4324286550651826</v>
       </c>
     </row>
@@ -758,29 +768,29 @@
         <v>80</v>
       </c>
       <c r="F4" s="2"/>
-      <c r="G4" s="3">
+      <c r="G4">
         <v>72</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4">
         <v>28</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4">
         <v>10</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4">
         <v>90</v>
       </c>
       <c r="K4" s="2"/>
-      <c r="L4" s="3">
+      <c r="L4">
         <v>66</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4">
         <v>34</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4">
         <v>26</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4">
         <v>74</v>
       </c>
       <c r="Q4">
@@ -862,53 +872,53 @@
         <v>89</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="3">
+      <c r="G5">
         <v>71</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5">
         <v>29</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5">
         <v>11</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5">
         <v>89</v>
       </c>
       <c r="K5" s="2"/>
-      <c r="L5" s="3">
+      <c r="L5">
         <v>55</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5">
         <v>45</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5">
         <v>18</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5">
         <v>82</v>
       </c>
       <c r="Q5">
-        <f t="shared" ref="Q5:Q10" si="0">AVERAGE(C5,D5)</f>
+        <f t="shared" ref="Q5:Q7" si="0">AVERAGE(C5,D5)</f>
         <v>15</v>
       </c>
       <c r="R5">
-        <f t="shared" ref="R5:R10" si="1">AVERAGE(H5,I5)</f>
+        <f t="shared" ref="R5:R7" si="1">AVERAGE(H5,I5)</f>
         <v>20</v>
       </c>
       <c r="S5">
-        <f t="shared" ref="S5:S10" si="2">AVERAGE(M5,N5)</f>
+        <f t="shared" ref="S5:S7" si="2">AVERAGE(M5,N5)</f>
         <v>31.5</v>
       </c>
       <c r="T5">
-        <f t="shared" ref="T5:T10" si="3">AVERAGE(Q5:S5)</f>
+        <f t="shared" ref="T5:T7" si="3">AVERAGE(Q5:S5)</f>
         <v>22.166666666666668</v>
       </c>
       <c r="U5">
-        <f t="shared" ref="U5:U10" si="4">MIN(Q5:S5)</f>
+        <f t="shared" ref="U5:U7" si="4">MIN(Q5:S5)</f>
         <v>15</v>
       </c>
       <c r="V5">
-        <f t="shared" ref="V5:V10" si="5">T5-U5</f>
+        <f t="shared" ref="V5:V7" si="5">T5-U5</f>
         <v>7.1666666666666679</v>
       </c>
     </row>
@@ -926,29 +936,29 @@
         <v>84</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="3">
+      <c r="G6">
         <v>69</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6">
         <v>31</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6">
         <v>3</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6">
         <v>97</v>
       </c>
       <c r="K6" s="2"/>
-      <c r="L6" s="3">
+      <c r="L6">
         <v>53</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6">
         <v>47</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6">
         <v>21</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6">
         <v>79</v>
       </c>
       <c r="Q6">
@@ -990,29 +1000,29 @@
         <v>84</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="3">
+      <c r="G7">
         <v>63</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7">
         <v>37</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7">
         <v>7</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7">
         <v>93</v>
       </c>
       <c r="K7" s="2"/>
-      <c r="L7" s="3">
+      <c r="L7">
         <v>65</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7">
         <v>35</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7">
         <v>21</v>
       </c>
-      <c r="O7" s="3">
+      <c r="O7">
         <v>79</v>
       </c>
       <c r="Q7">
@@ -1054,29 +1064,29 @@
         <v>80</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="3">
+      <c r="G8">
         <v>72</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8">
         <v>28</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8">
         <v>8</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8">
         <v>92</v>
       </c>
       <c r="K8" s="2"/>
-      <c r="L8" s="3">
+      <c r="L8">
         <v>64</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8">
         <v>36</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8">
         <v>31</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8">
         <v>69</v>
       </c>
       <c r="Q8">
@@ -1118,29 +1128,29 @@
         <v>82</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="3">
+      <c r="G9">
         <v>68</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9">
         <v>32</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9">
         <v>3</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9">
         <v>97</v>
       </c>
       <c r="K9" s="2"/>
-      <c r="L9" s="3">
+      <c r="L9">
         <v>71</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9">
         <v>29</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9">
         <v>29</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9">
         <v>71</v>
       </c>
       <c r="Q9">
@@ -1925,23 +1935,23 @@
         <v>80</v>
       </c>
       <c r="Q4">
-        <f t="shared" ref="Q4:Q67" si="0">AVERAGE(C4,D4)</f>
+        <f t="shared" ref="Q4:Q8" si="0">AVERAGE(C4,D4)</f>
         <v>13.5</v>
       </c>
       <c r="R4">
-        <f t="shared" ref="R4:R67" si="1">AVERAGE(H4:I4)</f>
+        <f t="shared" ref="R4:R8" si="1">AVERAGE(H4:I4)</f>
         <v>22.5</v>
       </c>
       <c r="S4">
-        <f t="shared" ref="S4:S67" si="2">AVERAGE(M4,N4)</f>
+        <f t="shared" ref="S4:S8" si="2">AVERAGE(M4,N4)</f>
         <v>30.5</v>
       </c>
       <c r="T4">
-        <f t="shared" ref="T4:T67" si="3">AVERAGE(Q4:S4)</f>
+        <f t="shared" ref="T4:T8" si="3">AVERAGE(Q4:S4)</f>
         <v>22.166666666666668</v>
       </c>
       <c r="U4">
-        <f t="shared" ref="U4:U67" si="4">MIN(Q4:S4)</f>
+        <f t="shared" ref="U4:U8" si="4">MIN(Q4:S4)</f>
         <v>13.5</v>
       </c>
       <c r="V4">
